--- a/dados/info_delegacias/dados_deams_comercial.xlsx
+++ b/dados/info_delegacias/dados_deams_comercial.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2927,7 +2927,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Garça</t>
+          <t>Leme</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Araras</t>
+          <t>Garça</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -2951,7 +2951,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Rio Claro</t>
+          <t>Araras</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Piracicaba</t>
+          <t>Rio Claro</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>São Manuel</t>
+          <t>Piracicaba</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Santa Bárbara d'Oeste</t>
+          <t>São Manuel</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Guaratinguetá</t>
+          <t>Santa Bárbara d'Oeste</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sumaré</t>
+          <t>Guaratinguetá</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Sumaré</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Pindamonhangaba</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ourinhos</t>
+          <t>Pindamonhangaba</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Capivari</t>
+          <t>Ourinhos</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Indaiatuba</t>
+          <t>Capivari</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Jundiaí</t>
+          <t>Indaiatuba</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Itu</t>
+          <t>Jundiaí</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Francisco Morato</t>
+          <t>Itu</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3131,7 +3131,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Jacareí</t>
+          <t>Francisco Morato</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3143,7 +3143,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Tatuí</t>
+          <t>Jacareí</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3155,7 +3155,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Santana de Parnaíba</t>
+          <t>Tatuí</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Barueri</t>
+          <t>Santana de Parnaíba</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Carapicuíba</t>
+          <t>Barueri</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3191,7 +3191,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Mogi das Cruzes</t>
+          <t>Carapicuíba</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Osasco</t>
+          <t>Mogi das Cruzes</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Itapevi</t>
+          <t>Osasco</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Votorantim</t>
+          <t>Itapevi</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3239,7 +3239,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Suzano</t>
+          <t>Votorantim</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Suzano</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Itapetininga</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Cotia</t>
+          <t>Itapetininga</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3287,7 +3287,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Taboão da Serra</t>
+          <t>Cotia</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -3299,7 +3299,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Cubatão</t>
+          <t>Taboão da Serra</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -3311,7 +3311,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>São Vicente</t>
+          <t>Cubatão</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Itapeva</t>
+          <t>São Vicente</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Praia Grande</t>
+          <t>Itapeva</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -3347,7 +3347,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Capão Bonito</t>
+          <t>Praia Grande</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Mongaguá</t>
+          <t>Capão Bonito</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Peruíbe</t>
+          <t>Mongaguá</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Registro</t>
+          <t>Peruíbe</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -3395,19 +3395,19 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Augustinópolis</t>
+          <t>Registro</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Araguatins</t>
+          <t>Dianópolis</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Tocantinópolis</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -3431,7 +3431,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Araguaína</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Colinas</t>
+          <t>Augustinópolis</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Guaraí</t>
+          <t>Araguatins</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -3467,7 +3467,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Paraíso do Tocantins</t>
+          <t>Tocantinópolis</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -3479,10 +3479,82 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
+          <t>Araguaína</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Colinas</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Guaraí</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Miracema do Tocantins</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Paraíso do Tocantins</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
           <t>Gurupi</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Arraias</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
